--- a/samples/tracking01/_general_display_test.xlsx
+++ b/samples/tracking01/_general_display_test.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>x</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>x</t>
         </is>
       </c>
     </row>
